--- a/public/templates/groups.xlsx
+++ b/public/templates/groups.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp1\htdocs\uwz\uwz\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F122A1D-0D90-4775-A47A-8B596F962C47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A353874-83EA-4DD3-B71C-DB5E087427E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{13E5B317-7678-4923-9096-6FD6968D18FB}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>date_formed</t>
   </si>
@@ -54,147 +54,6 @@
     <t>location</t>
   </si>
   <si>
-    <t>MZAWO WOMEN GROUP</t>
-  </si>
-  <si>
-    <t>MZA001</t>
-  </si>
-  <si>
-    <t>001</t>
-  </si>
-  <si>
-    <t>4-006-026-4110202-201-001</t>
-  </si>
-  <si>
-    <t>TTA/CD/2/3677</t>
-  </si>
-  <si>
-    <t>NULL</t>
-  </si>
-  <si>
-    <t>Women</t>
-  </si>
-  <si>
-    <t>Service</t>
-  </si>
-  <si>
-    <t>salons/ cosmetics</t>
-  </si>
-  <si>
-    <t>WIKWATYO WOMEN GRP</t>
-  </si>
-  <si>
-    <t>WIK002</t>
-  </si>
-  <si>
-    <t>002</t>
-  </si>
-  <si>
-    <t>4-006-026-4110202-102-002</t>
-  </si>
-  <si>
-    <t>TTA/CD/2/7116</t>
-  </si>
-  <si>
-    <t>Equity-Voi branch</t>
-  </si>
-  <si>
-    <t>1234567</t>
-  </si>
-  <si>
-    <t>Trade</t>
-  </si>
-  <si>
-    <t>Retail trade</t>
-  </si>
-  <si>
-    <t>Kasigau</t>
-  </si>
-  <si>
-    <t>DISCOVERY YOUTH GRP</t>
-  </si>
-  <si>
-    <t>DIS003</t>
-  </si>
-  <si>
-    <t>003</t>
-  </si>
-  <si>
-    <t>4-006-026-4110201-401-003</t>
-  </si>
-  <si>
-    <t>TTA/CD/2/5693</t>
-  </si>
-  <si>
-    <t>Youth</t>
-  </si>
-  <si>
-    <t>Livestock keeping, farming</t>
-  </si>
-  <si>
-    <t>MWANEDU SHG</t>
-  </si>
-  <si>
-    <t>MWA004</t>
-  </si>
-  <si>
-    <t>004</t>
-  </si>
-  <si>
-    <t>4-006-026-4110202-401-004</t>
-  </si>
-  <si>
-    <t>TTA/CD/2/8085</t>
-  </si>
-  <si>
-    <t>Rabbits, goat keeping</t>
-  </si>
-  <si>
-    <t>KILIMO NI BORA W.G.</t>
-  </si>
-  <si>
-    <t>KIL005</t>
-  </si>
-  <si>
-    <t>005</t>
-  </si>
-  <si>
-    <t>4-006-026-4110202-401-005</t>
-  </si>
-  <si>
-    <t>TTA/CD/2/6143</t>
-  </si>
-  <si>
-    <t>Tree seedlings, vegetables</t>
-  </si>
-  <si>
-    <t>Manufacturing</t>
-  </si>
-  <si>
-    <t>Kaloleni</t>
-  </si>
-  <si>
-    <t>Ngolia</t>
-  </si>
-  <si>
-    <t>Mbololo</t>
-  </si>
-  <si>
-    <t>Marungu</t>
-  </si>
-  <si>
-    <t>1234566</t>
-  </si>
-  <si>
-    <t>1234568</t>
-  </si>
-  <si>
-    <t>1234569</t>
-  </si>
-  <si>
-    <t>1234570</t>
-  </si>
-  <si>
     <t>ward*</t>
   </si>
   <si>
@@ -220,9 +79,6 @@
   </si>
   <si>
     <t>identifier</t>
-  </si>
-  <si>
-    <t>Other</t>
   </si>
 </sst>
 </file>
@@ -609,43 +465,50 @@
   <dimension ref="A1:P6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="15.6328125" customWidth="1"/>
-    <col min="4" max="4" width="8.7265625" style="4"/>
-    <col min="5" max="5" width="17.36328125" customWidth="1"/>
-    <col min="6" max="6" width="10.54296875" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.453125" style="4" customWidth="1"/>
-    <col min="8" max="9" width="8.7265625" style="4"/>
-    <col min="10" max="11" width="10.08984375" style="9" bestFit="1" customWidth="1"/>
-    <col min="12" max="15" width="8.7265625" style="4"/>
+    <col min="1" max="1" width="5.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.81640625" customWidth="1"/>
+    <col min="3" max="3" width="9.1796875" customWidth="1"/>
+    <col min="4" max="4" width="7.54296875" style="4" customWidth="1"/>
+    <col min="5" max="5" width="9.6328125" customWidth="1"/>
+    <col min="6" max="6" width="8.453125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.08984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.81640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.81640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.1796875" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.453125" style="4" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.54296875" style="4" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.54296875" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>53</v>
+        <v>6</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>56</v>
+        <v>9</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>57</v>
+        <v>10</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>61</v>
+        <v>14</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>58</v>
+        <v>11</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="J1" s="7" t="s">
         <v>0</v>
@@ -667,244 +530,94 @@
       </c>
       <c r="P1" s="1"/>
     </row>
-    <row r="2" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J2" s="8">
-        <v>42402</v>
-      </c>
-      <c r="K2" s="8">
-        <v>42410</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>11</v>
-      </c>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
       <c r="P2" s="1"/>
     </row>
-    <row r="3" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="2">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="J3" s="8">
-        <v>42403</v>
-      </c>
-      <c r="K3" s="8">
-        <v>42411</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>24</v>
-      </c>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
       <c r="P3" s="1"/>
     </row>
-    <row r="4" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="2">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J4" s="8">
-        <v>42404</v>
-      </c>
-      <c r="K4" s="8">
-        <v>42412</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>11</v>
-      </c>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
       <c r="P4" s="1"/>
     </row>
-    <row r="5" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="2">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="J5" s="8">
-        <v>42405</v>
-      </c>
-      <c r="K5" s="8">
-        <v>42413</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>11</v>
-      </c>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
       <c r="P5" s="1"/>
     </row>
-    <row r="6" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="2">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="J6" s="8">
-        <v>42406</v>
-      </c>
-      <c r="K6" s="8">
-        <v>42414</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="N6" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="O6" s="3" t="s">
-        <v>11</v>
-      </c>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
       <c r="P6" s="1"/>
     </row>
   </sheetData>
